--- a/output_phyto/phyto_Intermediate_badger_2013a.xlsx
+++ b/output_phyto/phyto_Intermediate_badger_2013a.xlsx
@@ -1454,13 +1454,13 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">phytoplankton_Badger_2013a_1</t>
+    <t xml:space="preserve">165-999A-10H-6W,48-50</t>
   </si>
   <si>
     <t xml:space="preserve">10.1098/rsta.2013.0094</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/phytoplankton_badger_2013a.xlsx</t>
+    <t xml:space="preserve">phytoplankton_badger_2013a_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
@@ -1475,88 +1475,88 @@
     <t xml:space="preserve">Mk37_2</t>
   </si>
   <si>
-    <t xml:space="preserve">alkenone unsaturation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Badger_2013a_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Badger_2013a_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Badger_2013a_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Badger_2013a_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Badger_2013a_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Badger_2013a_7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Badger_2013a_8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Badger_2013a_9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Badger_2013a_10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Badger_2013a_11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Badger_2013a_12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Badger_2013a_13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Badger_2013a_14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Badger_2013a_15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Badger_2013a_16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Badger_2013a_17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Badger_2013a_18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Badger_2013a_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Badger_2013a_20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Badger_2013a_21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Badger_2013a_22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Badger_2013a_23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Badger_2013a_24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Badger_2013a_25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Badger_2013a_26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Badger_2013a_27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Badger_2013a_28</t>
+    <t xml:space="preserve">published Uk37 temperature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-10H-7W,50-52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-10H-CCW,19-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-11H-1W,31-33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-11H-1W,88-90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-11H-1W,122-124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-11H-2W,27-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-11H-2W,139-141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-11H-3W,90-92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-11H-4W,3-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-11H-4W,63-65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-11H-5W,28-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-11H-5W,83-85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-11H-5W,112-114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-11H-5W,142-144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-11H-6W,68-70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-11H-7W,0-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-11H-7W,53-55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-11H-CCW,3-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-12H-1W,4-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-12H-1W,29-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-12H-1W,57-59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-12H-1W,118-120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-12H-2W,10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-12H-2W,29-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-12H-2W,50-52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-12H-2W,80-82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-999A-12H-2W,109.5-111.5</t>
   </si>
 </sst>
 </file>
@@ -1564,7 +1564,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1630,12 +1630,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1749,7 +1743,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1848,7 +1842,6 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2574,7 +2567,7 @@
       <c r="B5" t="s">
         <v>271</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" t="s">
         <v>272</v>
       </c>
       <c r="D5" t="s">
@@ -2592,8 +2585,8 @@
       <c r="H5" t="n">
         <v>2.80996</v>
       </c>
-      <c r="I5" t="e">
-        <v>#N/A</v>
+      <c r="I5" t="n">
+        <v>0.006</v>
       </c>
       <c r="J5" t="e">
         <v>#N/A</v>
@@ -2610,8 +2603,8 @@
       <c r="N5" t="n">
         <v>-23.06</v>
       </c>
-      <c r="O5" t="e">
-        <v>#N/A</v>
+      <c r="O5" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P5" t="e">
         <v>#N/A</v>
@@ -2623,7 +2616,7 @@
         <v>27.59</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T5" t="e">
         <v>#N/A</v>
@@ -2641,28 +2634,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA5" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB5" t="e">
-        <v>#N/A</v>
+      <c r="AB5" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC5" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF5" t="e">
-        <v>#N/A</v>
+      <c r="AD5" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG5" t="e">
         <v>#N/A</v>
@@ -2684,7 +2677,7 @@
       <c r="B6" t="s">
         <v>271</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" t="s">
         <v>272</v>
       </c>
       <c r="D6" t="s">
@@ -2702,8 +2695,8 @@
       <c r="H6" t="n">
         <v>2.8515</v>
       </c>
-      <c r="I6" t="e">
-        <v>#N/A</v>
+      <c r="I6" t="n">
+        <v>0.006</v>
       </c>
       <c r="J6" t="e">
         <v>#N/A</v>
@@ -2720,8 +2713,8 @@
       <c r="N6" t="n">
         <v>-23.61</v>
       </c>
-      <c r="O6" t="e">
-        <v>#N/A</v>
+      <c r="O6" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P6" t="e">
         <v>#N/A</v>
@@ -2733,7 +2726,7 @@
         <v>27.75</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T6" t="e">
         <v>#N/A</v>
@@ -2751,28 +2744,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA6" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB6" t="e">
-        <v>#N/A</v>
+      <c r="AB6" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC6" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF6" t="e">
-        <v>#N/A</v>
+      <c r="AD6" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG6" t="e">
         <v>#N/A</v>
@@ -2794,7 +2787,7 @@
       <c r="B7" t="s">
         <v>271</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" t="s">
         <v>272</v>
       </c>
       <c r="D7" t="s">
@@ -2812,8 +2805,8 @@
       <c r="H7" t="n">
         <v>2.8616</v>
       </c>
-      <c r="I7" t="e">
-        <v>#N/A</v>
+      <c r="I7" t="n">
+        <v>0.006</v>
       </c>
       <c r="J7" t="e">
         <v>#N/A</v>
@@ -2830,8 +2823,8 @@
       <c r="N7" t="n">
         <v>-23.27</v>
       </c>
-      <c r="O7" t="e">
-        <v>#N/A</v>
+      <c r="O7" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P7" t="e">
         <v>#N/A</v>
@@ -2843,7 +2836,7 @@
         <v>27.66</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T7" t="e">
         <v>#N/A</v>
@@ -2861,28 +2854,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA7" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB7" t="e">
-        <v>#N/A</v>
+      <c r="AB7" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC7" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF7" t="e">
-        <v>#N/A</v>
+      <c r="AD7" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG7" t="e">
         <v>#N/A</v>
@@ -2904,7 +2897,7 @@
       <c r="B8" t="s">
         <v>271</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" t="s">
         <v>272</v>
       </c>
       <c r="D8" t="s">
@@ -2922,8 +2915,8 @@
       <c r="H8" t="n">
         <v>2.90163</v>
       </c>
-      <c r="I8" t="e">
-        <v>#N/A</v>
+      <c r="I8" t="n">
+        <v>0.006</v>
       </c>
       <c r="J8" t="e">
         <v>#N/A</v>
@@ -2940,8 +2933,8 @@
       <c r="N8" t="n">
         <v>-22.48</v>
       </c>
-      <c r="O8" t="e">
-        <v>#N/A</v>
+      <c r="O8" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P8" t="e">
         <v>#N/A</v>
@@ -2953,7 +2946,7 @@
         <v>27.54</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T8" t="e">
         <v>#N/A</v>
@@ -2971,28 +2964,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA8" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB8" t="e">
-        <v>#N/A</v>
+      <c r="AB8" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC8" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF8" t="e">
-        <v>#N/A</v>
+      <c r="AD8" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG8" t="e">
         <v>#N/A</v>
@@ -3014,7 +3007,7 @@
       <c r="B9" t="s">
         <v>271</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" t="s">
         <v>272</v>
       </c>
       <c r="D9" t="s">
@@ -3032,8 +3025,8 @@
       <c r="H9" t="n">
         <v>2.91737</v>
       </c>
-      <c r="I9" t="e">
-        <v>#N/A</v>
+      <c r="I9" t="n">
+        <v>0.006</v>
       </c>
       <c r="J9" t="e">
         <v>#N/A</v>
@@ -3050,8 +3043,8 @@
       <c r="N9" t="n">
         <v>-23.16</v>
       </c>
-      <c r="O9" t="e">
-        <v>#N/A</v>
+      <c r="O9" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P9" t="e">
         <v>#N/A</v>
@@ -3063,7 +3056,7 @@
         <v>27.66</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T9" t="e">
         <v>#N/A</v>
@@ -3081,28 +3074,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA9" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB9" t="e">
-        <v>#N/A</v>
+      <c r="AB9" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC9" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF9" t="e">
-        <v>#N/A</v>
+      <c r="AD9" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG9" t="e">
         <v>#N/A</v>
@@ -3124,7 +3117,7 @@
       <c r="B10" t="s">
         <v>271</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" t="s">
         <v>272</v>
       </c>
       <c r="D10" t="s">
@@ -3142,8 +3135,8 @@
       <c r="H10" t="n">
         <v>2.9267</v>
       </c>
-      <c r="I10" t="e">
-        <v>#N/A</v>
+      <c r="I10" t="n">
+        <v>0.006</v>
       </c>
       <c r="J10" t="e">
         <v>#N/A</v>
@@ -3160,8 +3153,8 @@
       <c r="N10" t="n">
         <v>-22.78</v>
       </c>
-      <c r="O10" t="e">
-        <v>#N/A</v>
+      <c r="O10" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P10" t="e">
         <v>#N/A</v>
@@ -3173,7 +3166,7 @@
         <v>27.22</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T10" t="e">
         <v>#N/A</v>
@@ -3191,28 +3184,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA10" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB10" t="e">
-        <v>#N/A</v>
+      <c r="AB10" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC10" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF10" t="e">
-        <v>#N/A</v>
+      <c r="AD10" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG10" t="e">
         <v>#N/A</v>
@@ -3234,7 +3227,7 @@
       <c r="B11" t="s">
         <v>271</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="C11" t="s">
         <v>272</v>
       </c>
       <c r="D11" t="s">
@@ -3252,8 +3245,8 @@
       <c r="H11" t="n">
         <v>2.94364</v>
       </c>
-      <c r="I11" t="e">
-        <v>#N/A</v>
+      <c r="I11" t="n">
+        <v>0.006</v>
       </c>
       <c r="J11" t="e">
         <v>#N/A</v>
@@ -3270,8 +3263,8 @@
       <c r="N11" t="n">
         <v>-24.34</v>
       </c>
-      <c r="O11" t="e">
-        <v>#N/A</v>
+      <c r="O11" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P11" t="e">
         <v>#N/A</v>
@@ -3283,7 +3276,7 @@
         <v>27.64</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T11" t="e">
         <v>#N/A</v>
@@ -3301,28 +3294,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA11" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB11" t="e">
-        <v>#N/A</v>
+      <c r="AB11" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC11" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF11" t="e">
-        <v>#N/A</v>
+      <c r="AD11" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG11" t="e">
         <v>#N/A</v>
@@ -3344,7 +3337,7 @@
       <c r="B12" t="s">
         <v>271</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" t="s">
         <v>272</v>
       </c>
       <c r="D12" t="s">
@@ -3362,8 +3355,8 @@
       <c r="H12" t="n">
         <v>2.9807</v>
       </c>
-      <c r="I12" t="e">
-        <v>#N/A</v>
+      <c r="I12" t="n">
+        <v>0.006</v>
       </c>
       <c r="J12" t="e">
         <v>#N/A</v>
@@ -3380,8 +3373,8 @@
       <c r="N12" t="n">
         <v>-21.78</v>
       </c>
-      <c r="O12" t="e">
-        <v>#N/A</v>
+      <c r="O12" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P12" t="e">
         <v>#N/A</v>
@@ -3393,7 +3386,7 @@
         <v>27.69</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T12" t="e">
         <v>#N/A</v>
@@ -3411,28 +3404,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA12" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB12" t="e">
-        <v>#N/A</v>
+      <c r="AB12" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC12" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF12" t="e">
-        <v>#N/A</v>
+      <c r="AD12" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG12" t="e">
         <v>#N/A</v>
@@ -3454,7 +3447,7 @@
       <c r="B13" t="s">
         <v>271</v>
       </c>
-      <c r="C13" s="34" t="s">
+      <c r="C13" t="s">
         <v>272</v>
       </c>
       <c r="D13" t="s">
@@ -3472,8 +3465,8 @@
       <c r="H13" t="n">
         <v>3.00219</v>
       </c>
-      <c r="I13" t="e">
-        <v>#N/A</v>
+      <c r="I13" t="n">
+        <v>0.015</v>
       </c>
       <c r="J13" t="e">
         <v>#N/A</v>
@@ -3490,8 +3483,8 @@
       <c r="N13" t="n">
         <v>-21.84</v>
       </c>
-      <c r="O13" t="e">
-        <v>#N/A</v>
+      <c r="O13" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P13" t="e">
         <v>#N/A</v>
@@ -3503,7 +3496,7 @@
         <v>27.85</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T13" t="e">
         <v>#N/A</v>
@@ -3521,28 +3514,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA13" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB13" t="e">
-        <v>#N/A</v>
+      <c r="AB13" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC13" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF13" t="e">
-        <v>#N/A</v>
+      <c r="AD13" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG13" t="e">
         <v>#N/A</v>
@@ -3564,7 +3557,7 @@
       <c r="B14" t="s">
         <v>271</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="C14" t="s">
         <v>272</v>
       </c>
       <c r="D14" t="s">
@@ -3582,8 +3575,8 @@
       <c r="H14" t="n">
         <v>3.01618</v>
       </c>
-      <c r="I14" t="e">
-        <v>#N/A</v>
+      <c r="I14" t="n">
+        <v>0.015</v>
       </c>
       <c r="J14" t="e">
         <v>#N/A</v>
@@ -3600,8 +3593,8 @@
       <c r="N14" t="n">
         <v>-22.44</v>
       </c>
-      <c r="O14" t="e">
-        <v>#N/A</v>
+      <c r="O14" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P14" t="e">
         <v>#N/A</v>
@@ -3613,7 +3606,7 @@
         <v>27.57</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T14" t="e">
         <v>#N/A</v>
@@ -3631,28 +3624,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB14" t="e">
-        <v>#N/A</v>
+      <c r="AB14" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF14" t="e">
-        <v>#N/A</v>
+      <c r="AD14" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG14" t="e">
         <v>#N/A</v>
@@ -3674,7 +3667,7 @@
       <c r="B15" t="s">
         <v>271</v>
       </c>
-      <c r="C15" s="34" t="s">
+      <c r="C15" t="s">
         <v>272</v>
       </c>
       <c r="D15" t="s">
@@ -3692,8 +3685,8 @@
       <c r="H15" t="n">
         <v>3.03414</v>
       </c>
-      <c r="I15" t="e">
-        <v>#N/A</v>
+      <c r="I15" t="n">
+        <v>0.015</v>
       </c>
       <c r="J15" t="e">
         <v>#N/A</v>
@@ -3710,8 +3703,8 @@
       <c r="N15" t="n">
         <v>-21.9</v>
       </c>
-      <c r="O15" t="e">
-        <v>#N/A</v>
+      <c r="O15" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P15" t="e">
         <v>#N/A</v>
@@ -3723,7 +3716,7 @@
         <v>27.96</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T15" t="e">
         <v>#N/A</v>
@@ -3741,28 +3734,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA15" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB15" t="e">
-        <v>#N/A</v>
+      <c r="AB15" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC15" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF15" t="e">
-        <v>#N/A</v>
+      <c r="AD15" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG15" t="e">
         <v>#N/A</v>
@@ -3784,7 +3777,7 @@
       <c r="B16" t="s">
         <v>271</v>
       </c>
-      <c r="C16" s="34" t="s">
+      <c r="C16" t="s">
         <v>272</v>
       </c>
       <c r="D16" t="s">
@@ -3802,8 +3795,8 @@
       <c r="H16" t="n">
         <v>3.06914</v>
       </c>
-      <c r="I16" t="e">
-        <v>#N/A</v>
+      <c r="I16" t="n">
+        <v>0.015</v>
       </c>
       <c r="J16" t="e">
         <v>#N/A</v>
@@ -3820,8 +3813,8 @@
       <c r="N16" t="n">
         <v>-22.94</v>
       </c>
-      <c r="O16" t="e">
-        <v>#N/A</v>
+      <c r="O16" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P16" t="e">
         <v>#N/A</v>
@@ -3833,7 +3826,7 @@
         <v>28.19</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T16" t="e">
         <v>#N/A</v>
@@ -3851,28 +3844,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA16" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB16" t="e">
-        <v>#N/A</v>
+      <c r="AB16" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC16" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF16" t="e">
-        <v>#N/A</v>
+      <c r="AD16" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG16" t="e">
         <v>#N/A</v>
@@ -3894,7 +3887,7 @@
       <c r="B17" t="s">
         <v>271</v>
       </c>
-      <c r="C17" s="34" t="s">
+      <c r="C17" t="s">
         <v>272</v>
       </c>
       <c r="D17" t="s">
@@ -3912,8 +3905,8 @@
       <c r="H17" t="n">
         <v>3.08717</v>
       </c>
-      <c r="I17" t="e">
-        <v>#N/A</v>
+      <c r="I17" t="n">
+        <v>0.015</v>
       </c>
       <c r="J17" t="e">
         <v>#N/A</v>
@@ -3930,8 +3923,8 @@
       <c r="N17" t="n">
         <v>-21.45</v>
       </c>
-      <c r="O17" t="e">
-        <v>#N/A</v>
+      <c r="O17" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P17" t="e">
         <v>#N/A</v>
@@ -3943,7 +3936,7 @@
         <v>27.91</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T17" t="e">
         <v>#N/A</v>
@@ -3961,28 +3954,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB17" t="e">
-        <v>#N/A</v>
+      <c r="AB17" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF17" t="e">
-        <v>#N/A</v>
+      <c r="AD17" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG17" t="e">
         <v>#N/A</v>
@@ -4004,7 +3997,7 @@
       <c r="B18" t="s">
         <v>271</v>
       </c>
-      <c r="C18" s="34" t="s">
+      <c r="C18" t="s">
         <v>272</v>
       </c>
       <c r="D18" t="s">
@@ -4022,8 +4015,8 @@
       <c r="H18" t="n">
         <v>3.0963</v>
       </c>
-      <c r="I18" t="e">
-        <v>#N/A</v>
+      <c r="I18" t="n">
+        <v>0.015</v>
       </c>
       <c r="J18" t="e">
         <v>#N/A</v>
@@ -4040,8 +4033,8 @@
       <c r="N18" t="n">
         <v>-22.4</v>
       </c>
-      <c r="O18" t="e">
-        <v>#N/A</v>
+      <c r="O18" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P18" t="e">
         <v>#N/A</v>
@@ -4053,7 +4046,7 @@
         <v>28.72</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T18" t="e">
         <v>#N/A</v>
@@ -4071,28 +4064,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA18" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB18" t="e">
-        <v>#N/A</v>
+      <c r="AB18" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC18" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF18" t="e">
-        <v>#N/A</v>
+      <c r="AD18" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG18" t="e">
         <v>#N/A</v>
@@ -4114,7 +4107,7 @@
       <c r="B19" t="s">
         <v>271</v>
       </c>
-      <c r="C19" s="34" t="s">
+      <c r="C19" t="s">
         <v>272</v>
       </c>
       <c r="D19" t="s">
@@ -4132,8 +4125,8 @@
       <c r="H19" t="n">
         <v>3.10612</v>
       </c>
-      <c r="I19" t="e">
-        <v>#N/A</v>
+      <c r="I19" t="n">
+        <v>0.015</v>
       </c>
       <c r="J19" t="e">
         <v>#N/A</v>
@@ -4150,8 +4143,8 @@
       <c r="N19" t="n">
         <v>-22.44</v>
       </c>
-      <c r="O19" t="e">
-        <v>#N/A</v>
+      <c r="O19" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P19" t="e">
         <v>#N/A</v>
@@ -4163,7 +4156,7 @@
         <v>28.2</v>
       </c>
       <c r="S19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T19" t="e">
         <v>#N/A</v>
@@ -4181,28 +4174,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA19" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB19" t="e">
-        <v>#N/A</v>
+      <c r="AB19" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC19" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD19" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE19" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF19" t="e">
-        <v>#N/A</v>
+      <c r="AD19" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG19" t="e">
         <v>#N/A</v>
@@ -4224,7 +4217,7 @@
       <c r="B20" t="s">
         <v>271</v>
       </c>
-      <c r="C20" s="34" t="s">
+      <c r="C20" t="s">
         <v>272</v>
       </c>
       <c r="D20" t="s">
@@ -4242,8 +4235,8 @@
       <c r="H20" t="n">
         <v>3.13044</v>
       </c>
-      <c r="I20" t="e">
-        <v>#N/A</v>
+      <c r="I20" t="n">
+        <v>0.015</v>
       </c>
       <c r="J20" t="e">
         <v>#N/A</v>
@@ -4260,8 +4253,8 @@
       <c r="N20" t="n">
         <v>-22.84</v>
       </c>
-      <c r="O20" t="e">
-        <v>#N/A</v>
+      <c r="O20" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P20" t="e">
         <v>#N/A</v>
@@ -4273,7 +4266,7 @@
         <v>28.12</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T20" t="e">
         <v>#N/A</v>
@@ -4291,28 +4284,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA20" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB20" t="e">
-        <v>#N/A</v>
+      <c r="AB20" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC20" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF20" t="e">
-        <v>#N/A</v>
+      <c r="AD20" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG20" t="e">
         <v>#N/A</v>
@@ -4334,7 +4327,7 @@
       <c r="B21" t="s">
         <v>271</v>
       </c>
-      <c r="C21" s="34" t="s">
+      <c r="C21" t="s">
         <v>272</v>
       </c>
       <c r="D21" t="s">
@@ -4352,8 +4345,8 @@
       <c r="H21" t="n">
         <v>3.16057</v>
       </c>
-      <c r="I21" t="e">
-        <v>#N/A</v>
+      <c r="I21" t="n">
+        <v>0.015</v>
       </c>
       <c r="J21" t="e">
         <v>#N/A</v>
@@ -4370,8 +4363,8 @@
       <c r="N21" t="n">
         <v>-23.15</v>
       </c>
-      <c r="O21" t="e">
-        <v>#N/A</v>
+      <c r="O21" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P21" t="e">
         <v>#N/A</v>
@@ -4383,7 +4376,7 @@
         <v>27.9</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T21" t="e">
         <v>#N/A</v>
@@ -4401,28 +4394,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB21" t="e">
-        <v>#N/A</v>
+      <c r="AB21" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF21" t="e">
-        <v>#N/A</v>
+      <c r="AD21" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG21" t="e">
         <v>#N/A</v>
@@ -4444,7 +4437,7 @@
       <c r="B22" t="s">
         <v>271</v>
       </c>
-      <c r="C22" s="34" t="s">
+      <c r="C22" t="s">
         <v>272</v>
       </c>
       <c r="D22" t="s">
@@ -4462,8 +4455,8 @@
       <c r="H22" t="n">
         <v>3.1814</v>
       </c>
-      <c r="I22" t="e">
-        <v>#N/A</v>
+      <c r="I22" t="n">
+        <v>0.015</v>
       </c>
       <c r="J22" t="e">
         <v>#N/A</v>
@@ -4480,8 +4473,8 @@
       <c r="N22" t="n">
         <v>-21.97</v>
       </c>
-      <c r="O22" t="e">
-        <v>#N/A</v>
+      <c r="O22" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P22" t="e">
         <v>#N/A</v>
@@ -4493,7 +4486,7 @@
         <v>27.75</v>
       </c>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T22" t="e">
         <v>#N/A</v>
@@ -4511,28 +4504,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA22" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB22" t="e">
-        <v>#N/A</v>
+      <c r="AB22" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC22" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF22" t="e">
-        <v>#N/A</v>
+      <c r="AD22" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG22" t="e">
         <v>#N/A</v>
@@ -4554,7 +4547,7 @@
       <c r="B23" t="s">
         <v>271</v>
       </c>
-      <c r="C23" s="34" t="s">
+      <c r="C23" t="s">
         <v>272</v>
       </c>
       <c r="D23" t="s">
@@ -4572,8 +4565,8 @@
       <c r="H23" t="n">
         <v>3.1899</v>
       </c>
-      <c r="I23" t="e">
-        <v>#N/A</v>
+      <c r="I23" t="n">
+        <v>0.015</v>
       </c>
       <c r="J23" t="e">
         <v>#N/A</v>
@@ -4590,8 +4583,8 @@
       <c r="N23" t="n">
         <v>-22.75</v>
       </c>
-      <c r="O23" t="e">
-        <v>#N/A</v>
+      <c r="O23" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P23" t="e">
         <v>#N/A</v>
@@ -4603,7 +4596,7 @@
         <v>27.69</v>
       </c>
       <c r="S23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T23" t="e">
         <v>#N/A</v>
@@ -4621,28 +4614,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB23" t="e">
-        <v>#N/A</v>
+      <c r="AB23" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF23" t="e">
-        <v>#N/A</v>
+      <c r="AD23" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG23" t="e">
         <v>#N/A</v>
@@ -4664,7 +4657,7 @@
       <c r="B24" t="s">
         <v>271</v>
       </c>
-      <c r="C24" s="34" t="s">
+      <c r="C24" t="s">
         <v>272</v>
       </c>
       <c r="D24" t="s">
@@ -4682,8 +4675,8 @@
       <c r="H24" t="n">
         <v>3.19999</v>
       </c>
-      <c r="I24" t="e">
-        <v>#N/A</v>
+      <c r="I24" t="n">
+        <v>0.015</v>
       </c>
       <c r="J24" t="e">
         <v>#N/A</v>
@@ -4700,8 +4693,8 @@
       <c r="N24" t="n">
         <v>-22.38</v>
       </c>
-      <c r="O24" t="e">
-        <v>#N/A</v>
+      <c r="O24" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P24" t="e">
         <v>#N/A</v>
@@ -4713,7 +4706,7 @@
         <v>28.04</v>
       </c>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T24" t="e">
         <v>#N/A</v>
@@ -4731,28 +4724,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA24" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB24" t="e">
-        <v>#N/A</v>
+      <c r="AB24" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC24" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF24" t="e">
-        <v>#N/A</v>
+      <c r="AD24" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG24" t="e">
         <v>#N/A</v>
@@ -4774,7 +4767,7 @@
       <c r="B25" t="s">
         <v>271</v>
       </c>
-      <c r="C25" s="34" t="s">
+      <c r="C25" t="s">
         <v>272</v>
       </c>
       <c r="D25" t="s">
@@ -4792,8 +4785,8 @@
       <c r="H25" t="n">
         <v>3.20923</v>
       </c>
-      <c r="I25" t="e">
-        <v>#N/A</v>
+      <c r="I25" t="n">
+        <v>0.015</v>
       </c>
       <c r="J25" t="e">
         <v>#N/A</v>
@@ -4810,8 +4803,8 @@
       <c r="N25" t="n">
         <v>-22.2</v>
       </c>
-      <c r="O25" t="e">
-        <v>#N/A</v>
+      <c r="O25" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P25" t="e">
         <v>#N/A</v>
@@ -4823,7 +4816,7 @@
         <v>27.88</v>
       </c>
       <c r="S25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T25" t="e">
         <v>#N/A</v>
@@ -4841,28 +4834,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB25" t="e">
-        <v>#N/A</v>
+      <c r="AB25" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF25" t="e">
-        <v>#N/A</v>
+      <c r="AD25" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG25" t="e">
         <v>#N/A</v>
@@ -4884,7 +4877,7 @@
       <c r="B26" t="s">
         <v>271</v>
       </c>
-      <c r="C26" s="34" t="s">
+      <c r="C26" t="s">
         <v>272</v>
       </c>
       <c r="D26" t="s">
@@ -4902,8 +4895,8 @@
       <c r="H26" t="n">
         <v>3.22012</v>
       </c>
-      <c r="I26" t="e">
-        <v>#N/A</v>
+      <c r="I26" t="n">
+        <v>0.015</v>
       </c>
       <c r="J26" t="e">
         <v>#N/A</v>
@@ -4920,8 +4913,8 @@
       <c r="N26" t="n">
         <v>-21.8</v>
       </c>
-      <c r="O26" t="e">
-        <v>#N/A</v>
+      <c r="O26" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P26" t="e">
         <v>#N/A</v>
@@ -4933,7 +4926,7 @@
         <v>27.93</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T26" t="e">
         <v>#N/A</v>
@@ -4951,28 +4944,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA26" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB26" t="e">
-        <v>#N/A</v>
+      <c r="AB26" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC26" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF26" t="e">
-        <v>#N/A</v>
+      <c r="AD26" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG26" t="e">
         <v>#N/A</v>
@@ -4994,7 +4987,7 @@
       <c r="B27" t="s">
         <v>271</v>
       </c>
-      <c r="C27" s="34" t="s">
+      <c r="C27" t="s">
         <v>272</v>
       </c>
       <c r="D27" t="s">
@@ -5012,8 +5005,8 @@
       <c r="H27" t="n">
         <v>3.24333</v>
       </c>
-      <c r="I27" t="e">
-        <v>#N/A</v>
+      <c r="I27" t="n">
+        <v>0.015</v>
       </c>
       <c r="J27" t="e">
         <v>#N/A</v>
@@ -5030,8 +5023,8 @@
       <c r="N27" t="n">
         <v>-22.47</v>
       </c>
-      <c r="O27" t="e">
-        <v>#N/A</v>
+      <c r="O27" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P27" t="e">
         <v>#N/A</v>
@@ -5043,7 +5036,7 @@
         <v>27.79</v>
       </c>
       <c r="S27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T27" t="e">
         <v>#N/A</v>
@@ -5061,28 +5054,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA27" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB27" t="e">
-        <v>#N/A</v>
+      <c r="AB27" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC27" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD27" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE27" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF27" t="e">
-        <v>#N/A</v>
+      <c r="AD27" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG27" t="e">
         <v>#N/A</v>
@@ -5104,7 +5097,7 @@
       <c r="B28" t="s">
         <v>271</v>
       </c>
-      <c r="C28" s="34" t="s">
+      <c r="C28" t="s">
         <v>272</v>
       </c>
       <c r="D28" t="s">
@@ -5122,8 +5115,8 @@
       <c r="H28" t="n">
         <v>3.25975</v>
       </c>
-      <c r="I28" t="e">
-        <v>#N/A</v>
+      <c r="I28" t="n">
+        <v>0.015</v>
       </c>
       <c r="J28" t="e">
         <v>#N/A</v>
@@ -5140,8 +5133,8 @@
       <c r="N28" t="n">
         <v>-22.28</v>
       </c>
-      <c r="O28" t="e">
-        <v>#N/A</v>
+      <c r="O28" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P28" t="e">
         <v>#N/A</v>
@@ -5153,7 +5146,7 @@
         <v>28.17</v>
       </c>
       <c r="S28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T28" t="e">
         <v>#N/A</v>
@@ -5171,28 +5164,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA28" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB28" t="e">
-        <v>#N/A</v>
+      <c r="AB28" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC28" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF28" t="e">
-        <v>#N/A</v>
+      <c r="AD28" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG28" t="e">
         <v>#N/A</v>
@@ -5214,7 +5207,7 @@
       <c r="B29" t="s">
         <v>271</v>
       </c>
-      <c r="C29" s="34" t="s">
+      <c r="C29" t="s">
         <v>272</v>
       </c>
       <c r="D29" t="s">
@@ -5232,8 +5225,8 @@
       <c r="H29" t="n">
         <v>3.2671</v>
       </c>
-      <c r="I29" t="e">
-        <v>#N/A</v>
+      <c r="I29" t="n">
+        <v>0.015</v>
       </c>
       <c r="J29" t="e">
         <v>#N/A</v>
@@ -5250,8 +5243,8 @@
       <c r="N29" t="n">
         <v>-21.73</v>
       </c>
-      <c r="O29" t="e">
-        <v>#N/A</v>
+      <c r="O29" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P29" t="e">
         <v>#N/A</v>
@@ -5263,7 +5256,7 @@
         <v>28.16</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T29" t="e">
         <v>#N/A</v>
@@ -5281,28 +5274,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA29" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB29" t="e">
-        <v>#N/A</v>
+      <c r="AB29" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC29" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF29" t="e">
-        <v>#N/A</v>
+      <c r="AD29" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG29" t="e">
         <v>#N/A</v>
@@ -5324,7 +5317,7 @@
       <c r="B30" t="s">
         <v>271</v>
       </c>
-      <c r="C30" s="34" t="s">
+      <c r="C30" t="s">
         <v>272</v>
       </c>
       <c r="D30" t="s">
@@ -5342,8 +5335,8 @@
       <c r="H30" t="n">
         <v>3.27526</v>
       </c>
-      <c r="I30" t="e">
-        <v>#N/A</v>
+      <c r="I30" t="n">
+        <v>0.015</v>
       </c>
       <c r="J30" t="e">
         <v>#N/A</v>
@@ -5360,8 +5353,8 @@
       <c r="N30" t="n">
         <v>-21.5</v>
       </c>
-      <c r="O30" t="e">
-        <v>#N/A</v>
+      <c r="O30" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P30" t="e">
         <v>#N/A</v>
@@ -5373,7 +5366,7 @@
         <v>28.15</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T30" t="e">
         <v>#N/A</v>
@@ -5391,28 +5384,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA30" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB30" t="e">
-        <v>#N/A</v>
+      <c r="AB30" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC30" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD30" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE30" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF30" t="e">
-        <v>#N/A</v>
+      <c r="AD30" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG30" t="e">
         <v>#N/A</v>
@@ -5434,7 +5427,7 @@
       <c r="B31" t="s">
         <v>271</v>
       </c>
-      <c r="C31" s="34" t="s">
+      <c r="C31" t="s">
         <v>272</v>
       </c>
       <c r="D31" t="s">
@@ -5452,8 +5445,8 @@
       <c r="H31" t="n">
         <v>3.28675</v>
       </c>
-      <c r="I31" t="e">
-        <v>#N/A</v>
+      <c r="I31" t="n">
+        <v>0.015</v>
       </c>
       <c r="J31" t="e">
         <v>#N/A</v>
@@ -5470,8 +5463,8 @@
       <c r="N31" t="n">
         <v>-22.5</v>
       </c>
-      <c r="O31" t="e">
-        <v>#N/A</v>
+      <c r="O31" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P31" t="e">
         <v>#N/A</v>
@@ -5483,7 +5476,7 @@
         <v>28.13</v>
       </c>
       <c r="S31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T31" t="e">
         <v>#N/A</v>
@@ -5501,28 +5494,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA31" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB31" t="e">
-        <v>#N/A</v>
+      <c r="AB31" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC31" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF31" t="e">
-        <v>#N/A</v>
+      <c r="AD31" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG31" t="e">
         <v>#N/A</v>
@@ -5544,7 +5537,7 @@
       <c r="B32" t="s">
         <v>271</v>
       </c>
-      <c r="C32" s="34" t="s">
+      <c r="C32" t="s">
         <v>272</v>
       </c>
       <c r="D32" t="s">
@@ -5562,8 +5555,8 @@
       <c r="H32" t="n">
         <v>3.29814</v>
       </c>
-      <c r="I32" t="e">
-        <v>#N/A</v>
+      <c r="I32" t="n">
+        <v>0.015</v>
       </c>
       <c r="J32" t="e">
         <v>#N/A</v>
@@ -5593,7 +5586,7 @@
         <v>28.12</v>
       </c>
       <c r="S32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T32" t="e">
         <v>#N/A</v>
@@ -5611,10 +5604,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA32" t="e">
         <v>#N/A</v>
@@ -5949,36 +5942,6 @@
       <formula>#REF!="no"</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1h"/>
-    <hyperlink ref="C6" r:id="rId2h"/>
-    <hyperlink ref="C7" r:id="rId3h"/>
-    <hyperlink ref="C8" r:id="rId4h"/>
-    <hyperlink ref="C9" r:id="rId5h"/>
-    <hyperlink ref="C10" r:id="rId6h"/>
-    <hyperlink ref="C11" r:id="rId7h"/>
-    <hyperlink ref="C12" r:id="rId8h"/>
-    <hyperlink ref="C13" r:id="rId9h"/>
-    <hyperlink ref="C14" r:id="rId10h"/>
-    <hyperlink ref="C15" r:id="rId11h"/>
-    <hyperlink ref="C16" r:id="rId12h"/>
-    <hyperlink ref="C17" r:id="rId13h"/>
-    <hyperlink ref="C18" r:id="rId14h"/>
-    <hyperlink ref="C19" r:id="rId15h"/>
-    <hyperlink ref="C20" r:id="rId16h"/>
-    <hyperlink ref="C21" r:id="rId17h"/>
-    <hyperlink ref="C22" r:id="rId18h"/>
-    <hyperlink ref="C23" r:id="rId19h"/>
-    <hyperlink ref="C24" r:id="rId20h"/>
-    <hyperlink ref="C25" r:id="rId21h"/>
-    <hyperlink ref="C26" r:id="rId22h"/>
-    <hyperlink ref="C27" r:id="rId23h"/>
-    <hyperlink ref="C28" r:id="rId24h"/>
-    <hyperlink ref="C29" r:id="rId25h"/>
-    <hyperlink ref="C30" r:id="rId26h"/>
-    <hyperlink ref="C31" r:id="rId27h"/>
-    <hyperlink ref="C32" r:id="rId28h"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
